--- a/artfynd/A 21797-2022 artfynd.xlsx
+++ b/artfynd/A 21797-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21797-2022 artfynd.xlsx
+++ b/artfynd/A 21797-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100101395</v>
+        <v>100101394</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
+        <v>89356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,25 +1155,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563347.1654861615</v>
+        <v>563293.8100068227</v>
       </c>
       <c r="R6" t="n">
-        <v>6862344.520570048</v>
+        <v>6862368.998977416</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,123 +1257,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>100101394</v>
-      </c>
-      <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Ljusdal-Ramsjö, Hls</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>563293.8100068227</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6862368.998977416</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2021-11-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2021-11-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
